--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,6701 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126434369</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>593159</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6972583</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126434277</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>593185</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6972629</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126434192</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>593208</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972678</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126433161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>593134</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972832</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126430961</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>593369</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972715</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av dom inom området</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126439888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>593426</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972735</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126439875</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>593130</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972732</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126434624</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91538</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>593248</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6972573</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126439876</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>593138</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6972753</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126439906</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>593425</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6972739</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126433197</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>593134</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6972832</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126433726</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>593198</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6972731</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126439892</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80109</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>593354</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6972776</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126439904</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>593135</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6972820</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126439908</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>593358</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6972766</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 ex</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126439896</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58025</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>593366</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6972772</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126434180</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>593208</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6972678</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126439893</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97230</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>593361</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6972794</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126439885</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>593381</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6972788</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126430580</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>593384</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6972679</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, äldre ringhack + äldre ringhack som har återanvänts.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126439891</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>593397</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6972760</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Lockläte övriga läten</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126431424</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80080</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>593306</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6972805</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126433941</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>593229</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6972713</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126439872</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>593156</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6972717</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126439897</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>593137</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6972822</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>60 ex</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126430999</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58025</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>593357</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6972730</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126439881</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>593155</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6972813</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126439884</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>593373</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6972785</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126434589</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>593238</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6972567</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126434241</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>593202</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6972629</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126432904</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>593235</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6972896</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126439880</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>593149</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6972772</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126439898</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>593306</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6972813</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>70 ex</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126439887</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>593434</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6972745</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126439871</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>593164</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6972685</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126433556</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>593175</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6972765</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126432147</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>593250</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6972871</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126431305</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>593333</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6972791</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126430758</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>593375</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6972676</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126434208</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>593200</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6972665</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126434119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>593241</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6972676</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126439867</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>593250</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6972866</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126439866</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91207</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>593407</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6972756</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126439905</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>593134</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6972823</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126439883</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>593342</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6972786</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126430348</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>593407</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6972697</v>
+      </c>
+      <c r="S49" t="n">
+        <v>18</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126434358</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91242</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>593134</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6972597</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126439882</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>593280</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6972844</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126430873</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>593384</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6972679</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av dom</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126439902</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>593267</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6972859</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126439895</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80108</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>593299</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6972823</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126439869</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>593194</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6972622</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126439868</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>593219</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6972646</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126439889</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>593443</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6972717</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126439878</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>593144</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6972760</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126439873</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>593152</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6972714</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126433598</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98269</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>593170</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6972741</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126434452</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>593205</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6972593</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126439901</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>593249</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6972870</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126439907</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>593396</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6972786</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126433689</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>593188</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6972729</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126431085</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fisklössjöflon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>593369</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6972715</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126439886</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>593386</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6972774</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126439874</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>593158</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6972739</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126434201</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>593201</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6972667</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126434333</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fisklössjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>593160</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6972621</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -2501,49 +2501,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126434180</v>
+        <v>126439893</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>97230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593208</v>
+        <v>593361</v>
       </c>
       <c r="R20" t="n">
-        <v>6972678</v>
+        <v>6972794</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,32 +2598,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126439893</v>
+        <v>126439885</v>
       </c>
       <c r="B21" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2637,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593361</v>
+        <v>593381</v>
       </c>
       <c r="R21" t="n">
-        <v>6972794</v>
+        <v>6972788</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,6 +2669,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,45 +2700,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126439885</v>
+        <v>126434180</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593381</v>
+        <v>593208</v>
       </c>
       <c r="R22" t="n">
-        <v>6972788</v>
+        <v>6972678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2770,11 +2775,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3418,50 +3418,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126430999</v>
+        <v>126434589</v>
       </c>
       <c r="B29" t="n">
-        <v>58025</v>
+        <v>91242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593357</v>
+        <v>593238</v>
       </c>
       <c r="R29" t="n">
-        <v>6972730</v>
+        <v>6972567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3520,27 +3515,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126439881</v>
+        <v>126430999</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>58025</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3549,16 +3544,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593155</v>
+        <v>593357</v>
       </c>
       <c r="R30" t="n">
-        <v>6972813</v>
+        <v>6972730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,11 +3591,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3622,7 +3617,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126439884</v>
+        <v>126439881</v>
       </c>
       <c r="B31" t="n">
         <v>57656</v>
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593373</v>
+        <v>593155</v>
       </c>
       <c r="R31" t="n">
-        <v>6972785</v>
+        <v>6972813</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3724,10 +3719,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126434589</v>
+        <v>126439884</v>
       </c>
       <c r="B32" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,21 +3730,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3759,10 +3754,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593238</v>
+        <v>593373</v>
       </c>
       <c r="R32" t="n">
-        <v>6972567</v>
+        <v>6972785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,6 +3790,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4545,45 +4545,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126432147</v>
+        <v>126430758</v>
       </c>
       <c r="B40" t="n">
-        <v>91260</v>
+        <v>98269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593250</v>
+        <v>593375</v>
       </c>
       <c r="R40" t="n">
-        <v>6972871</v>
+        <v>6972676</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,7 +4642,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126431305</v>
+        <v>126432147</v>
       </c>
       <c r="B41" t="n">
         <v>91260</v>
@@ -4673,14 +4673,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593333</v>
+        <v>593250</v>
       </c>
       <c r="R41" t="n">
-        <v>6972791</v>
+        <v>6972871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,32 +4739,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126430758</v>
+        <v>126431305</v>
       </c>
       <c r="B42" t="n">
-        <v>98269</v>
+        <v>91260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4774,10 +4774,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593375</v>
+        <v>593333</v>
       </c>
       <c r="R42" t="n">
-        <v>6972676</v>
+        <v>6972791</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4836,10 +4836,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126434208</v>
+        <v>126439867</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593200</v>
+        <v>593250</v>
       </c>
       <c r="R43" t="n">
-        <v>6972665</v>
+        <v>6972866</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,50 +4933,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126434119</v>
+        <v>126439866</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>91207</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593241</v>
+        <v>593407</v>
       </c>
       <c r="R44" t="n">
-        <v>6972676</v>
+        <v>6972756</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5009,11 +5004,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5040,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126439867</v>
+        <v>126434208</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593250</v>
+        <v>593200</v>
       </c>
       <c r="R45" t="n">
-        <v>6972866</v>
+        <v>6972665</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5137,45 +5127,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126439866</v>
+        <v>126434119</v>
       </c>
       <c r="B46" t="n">
-        <v>91207</v>
+        <v>57656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593407</v>
+        <v>593241</v>
       </c>
       <c r="R46" t="n">
-        <v>6972756</v>
+        <v>6972676</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5208,6 +5203,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5637,45 +5637,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126439882</v>
+        <v>126430873</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>593280</v>
+        <v>593384</v>
       </c>
       <c r="R51" t="n">
-        <v>6972844</v>
+        <v>6972679</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5712,7 +5716,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av dom</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5739,49 +5743,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126430873</v>
+        <v>126439882</v>
       </c>
       <c r="B52" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>593384</v>
+        <v>593280</v>
       </c>
       <c r="R52" t="n">
-        <v>6972679</v>
+        <v>6972844</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6447,32 +6447,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126439873</v>
+        <v>126433598</v>
       </c>
       <c r="B59" t="n">
-        <v>57656</v>
+        <v>98269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>593152</v>
+        <v>593170</v>
       </c>
       <c r="R59" t="n">
-        <v>6972714</v>
+        <v>6972741</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6518,11 +6518,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6549,32 +6544,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126433598</v>
+        <v>126439873</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>57656</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>593170</v>
+        <v>593152</v>
       </c>
       <c r="R60" t="n">
-        <v>6972741</v>
+        <v>6972714</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,6 +6615,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126434369</v>
+        <v>126430961</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593159</v>
+        <v>593369</v>
       </c>
       <c r="R4" t="n">
-        <v>6972583</v>
+        <v>6972715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst av dom inom området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126434277</v>
+        <v>126434369</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,7 +1012,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593185</v>
+        <v>593159</v>
       </c>
       <c r="R5" t="n">
-        <v>6972629</v>
+        <v>6972583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126434192</v>
+        <v>126434277</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,7 +1119,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593208</v>
+        <v>593185</v>
       </c>
       <c r="R6" t="n">
-        <v>6972678</v>
+        <v>6972629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,45 +1195,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126433161</v>
+        <v>126434192</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593134</v>
+        <v>593208</v>
       </c>
       <c r="R7" t="n">
-        <v>6972832</v>
+        <v>6972678</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,45 +1302,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126430961</v>
+        <v>126433161</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593369</v>
+        <v>593134</v>
       </c>
       <c r="R8" t="n">
-        <v>6972715</v>
+        <v>6972832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom inom området</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,7 +1407,7 @@
         <v>126439888</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>126439875</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126434624</v>
+        <v>126439906</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593248</v>
+        <v>593425</v>
       </c>
       <c r="R11" t="n">
-        <v>6972573</v>
+        <v>6972739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
         <v>126439876</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126439906</v>
+        <v>126434624</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593425</v>
+        <v>593248</v>
       </c>
       <c r="R13" t="n">
-        <v>6972739</v>
+        <v>6972573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,32 +1904,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126433197</v>
+        <v>126439892</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>80112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593134</v>
+        <v>593354</v>
       </c>
       <c r="R14" t="n">
-        <v>6972832</v>
+        <v>6972776</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1975,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126433726</v>
+        <v>126433197</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593198</v>
+        <v>593134</v>
       </c>
       <c r="R15" t="n">
-        <v>6972731</v>
+        <v>6972832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,32 +2103,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126439892</v>
+        <v>126433726</v>
       </c>
       <c r="B16" t="n">
-        <v>80109</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593354</v>
+        <v>593198</v>
       </c>
       <c r="R16" t="n">
-        <v>6972776</v>
+        <v>6972731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2174,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,32 +2205,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126439904</v>
+        <v>126439896</v>
       </c>
       <c r="B17" t="n">
-        <v>91260</v>
+        <v>58027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593135</v>
+        <v>593366</v>
       </c>
       <c r="R17" t="n">
-        <v>6972820</v>
+        <v>6972772</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126439908</v>
+        <v>126439904</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>91263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593358</v>
+        <v>593135</v>
       </c>
       <c r="R18" t="n">
-        <v>6972766</v>
+        <v>6972820</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2373,11 +2373,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126439896</v>
+        <v>126439908</v>
       </c>
       <c r="B19" t="n">
-        <v>58025</v>
+        <v>98278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,21 +2410,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2439,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593366</v>
+        <v>593358</v>
       </c>
       <c r="R19" t="n">
-        <v>6972772</v>
+        <v>6972766</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,6 +2470,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,32 +2501,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126439893</v>
+        <v>126439885</v>
       </c>
       <c r="B20" t="n">
-        <v>97230</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593361</v>
+        <v>593381</v>
       </c>
       <c r="R20" t="n">
-        <v>6972794</v>
+        <v>6972788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,6 +2572,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,45 +2603,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126439885</v>
+        <v>126434180</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593381</v>
+        <v>593208</v>
       </c>
       <c r="R21" t="n">
-        <v>6972788</v>
+        <v>6972678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2669,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2700,49 +2704,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126434180</v>
+        <v>126439893</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>97239</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593208</v>
+        <v>593361</v>
       </c>
       <c r="R22" t="n">
-        <v>6972678</v>
+        <v>6972794</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2804,7 +2804,7 @@
         <v>126430580</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126439891</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>126431424</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>126433941</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>126439872</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>126439897</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126434589</v>
       </c>
       <c r="B29" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>126430999</v>
       </c>
       <c r="B30" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>126439881</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>126439884</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>126434241</v>
       </c>
       <c r="B33" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126432904</v>
+        <v>126439880</v>
       </c>
       <c r="B34" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>593235</v>
+        <v>593149</v>
       </c>
       <c r="R34" t="n">
-        <v>6972896</v>
+        <v>6972772</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,10 +4030,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126439880</v>
+        <v>126439887</v>
       </c>
       <c r="B35" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593149</v>
+        <v>593434</v>
       </c>
       <c r="R35" t="n">
-        <v>6972772</v>
+        <v>6972745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126439898</v>
+        <v>126432904</v>
       </c>
       <c r="B36" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593306</v>
+        <v>593235</v>
       </c>
       <c r="R36" t="n">
-        <v>6972813</v>
+        <v>6972896</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4234,10 +4234,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126439887</v>
+        <v>126439871</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593434</v>
+        <v>593164</v>
       </c>
       <c r="R37" t="n">
-        <v>6972745</v>
+        <v>6972685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,32 +4336,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126439871</v>
+        <v>126439898</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593164</v>
+        <v>593306</v>
       </c>
       <c r="R38" t="n">
-        <v>6972685</v>
+        <v>6972813</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4441,7 +4441,7 @@
         <v>126433556</v>
       </c>
       <c r="B39" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>126430758</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>126432147</v>
       </c>
       <c r="B41" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>126431305</v>
       </c>
       <c r="B42" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>126439867</v>
       </c>
       <c r="B43" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,45 +4933,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126439866</v>
+        <v>126434119</v>
       </c>
       <c r="B44" t="n">
-        <v>91207</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593407</v>
+        <v>593241</v>
       </c>
       <c r="R44" t="n">
-        <v>6972756</v>
+        <v>6972676</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5004,6 +5009,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5030,32 +5040,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126434208</v>
+        <v>126439866</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>91210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>593200</v>
+        <v>593407</v>
       </c>
       <c r="R45" t="n">
-        <v>6972665</v>
+        <v>6972756</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5127,10 +5137,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126434119</v>
+        <v>126434208</v>
       </c>
       <c r="B46" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5138,39 +5148,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>593241</v>
+        <v>593200</v>
       </c>
       <c r="R46" t="n">
-        <v>6972676</v>
+        <v>6972665</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5203,11 +5208,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5237,7 +5237,7 @@
         <v>126439905</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126439883</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>126430348</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>126434358</v>
       </c>
       <c r="B50" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>126430873</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>126439882</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>126439902</v>
       </c>
       <c r="B53" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5942,32 +5942,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126439895</v>
+        <v>126439869</v>
       </c>
       <c r="B54" t="n">
-        <v>80108</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593299</v>
+        <v>593194</v>
       </c>
       <c r="R54" t="n">
-        <v>6972823</v>
+        <v>6972622</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6013,6 +6013,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6039,10 +6044,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126439869</v>
+        <v>126439868</v>
       </c>
       <c r="B55" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>593194</v>
+        <v>593219</v>
       </c>
       <c r="R55" t="n">
-        <v>6972622</v>
+        <v>6972646</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6114,7 +6119,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,32 +6146,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126439868</v>
+        <v>126439895</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>80111</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6176,10 +6181,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>593219</v>
+        <v>593299</v>
       </c>
       <c r="R56" t="n">
-        <v>6972646</v>
+        <v>6972823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,11 +6217,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6246,7 +6246,7 @@
         <v>126439889</v>
       </c>
       <c r="B57" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>126439878</v>
       </c>
       <c r="B58" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6447,32 +6447,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126433598</v>
+        <v>126439873</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>593170</v>
+        <v>593152</v>
       </c>
       <c r="R59" t="n">
-        <v>6972741</v>
+        <v>6972714</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6518,6 +6518,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6544,32 +6549,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126439873</v>
+        <v>126433598</v>
       </c>
       <c r="B60" t="n">
-        <v>57656</v>
+        <v>98278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>593152</v>
+        <v>593170</v>
       </c>
       <c r="R60" t="n">
-        <v>6972714</v>
+        <v>6972741</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,11 +6620,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6649,7 +6649,7 @@
         <v>126434452</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>126439901</v>
       </c>
       <c r="B62" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>126439907</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126433689</v>
+        <v>126434201</v>
       </c>
       <c r="B64" t="n">
-        <v>57656</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,27 +6958,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>593188</v>
+        <v>593201</v>
       </c>
       <c r="R64" t="n">
-        <v>6972729</v>
+        <v>6972667</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7023,11 +7023,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7054,10 +7049,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126431085</v>
+        <v>126433689</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7090,14 +7085,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>593369</v>
+        <v>593188</v>
       </c>
       <c r="R65" t="n">
-        <v>6972715</v>
+        <v>6972729</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7134,7 +7129,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7161,10 +7156,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126439886</v>
+        <v>126431085</v>
       </c>
       <c r="B66" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7190,16 +7185,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>593386</v>
+        <v>593369</v>
       </c>
       <c r="R66" t="n">
-        <v>6972774</v>
+        <v>6972715</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126439874</v>
+        <v>126434333</v>
       </c>
       <c r="B67" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7292,16 +7292,21 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>593158</v>
+        <v>593160</v>
       </c>
       <c r="R67" t="n">
-        <v>6972739</v>
+        <v>6972621</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7338,7 +7343,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7365,10 +7370,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126434201</v>
+        <v>126439886</v>
       </c>
       <c r="B68" t="n">
-        <v>57816</v>
+        <v>57657</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,39 +7381,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>593201</v>
+        <v>593386</v>
       </c>
       <c r="R68" t="n">
-        <v>6972667</v>
+        <v>6972774</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7441,6 +7441,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7467,10 +7472,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126434333</v>
+        <v>126439874</v>
       </c>
       <c r="B69" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7496,21 +7501,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>593160</v>
+        <v>593158</v>
       </c>
       <c r="R69" t="n">
-        <v>6972621</v>
+        <v>6972739</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126439906</v>
+        <v>126434624</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593425</v>
+        <v>593248</v>
       </c>
       <c r="R11" t="n">
-        <v>6972739</v>
+        <v>6972573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126439876</v>
+        <v>126439906</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593138</v>
+        <v>593425</v>
       </c>
       <c r="R12" t="n">
-        <v>6972753</v>
+        <v>6972739</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126434624</v>
+        <v>126439876</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593248</v>
+        <v>593138</v>
       </c>
       <c r="R13" t="n">
-        <v>6972573</v>
+        <v>6972753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2908,10 +2908,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126439891</v>
+        <v>126431424</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,34 +2919,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593397</v>
+        <v>593306</v>
       </c>
       <c r="R24" t="n">
-        <v>6972760</v>
+        <v>6972805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,11 +2979,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lockläte övriga läten</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3010,10 +3005,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126431424</v>
+        <v>126439891</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>57817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3021,34 +3016,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>593306</v>
+        <v>593397</v>
       </c>
       <c r="R25" t="n">
-        <v>6972805</v>
+        <v>6972760</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,6 +3076,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Lockläte övriga läten</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126434589</v>
+        <v>126439881</v>
       </c>
       <c r="B29" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593238</v>
+        <v>593155</v>
       </c>
       <c r="R29" t="n">
-        <v>6972567</v>
+        <v>6972813</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,6 +3489,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3515,27 +3520,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126430999</v>
+        <v>126439884</v>
       </c>
       <c r="B30" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3544,21 +3549,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593357</v>
+        <v>593373</v>
       </c>
       <c r="R30" t="n">
-        <v>6972730</v>
+        <v>6972785</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3591,6 +3591,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3617,10 +3622,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126439881</v>
+        <v>126434589</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3628,21 +3633,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3657,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593155</v>
+        <v>593238</v>
       </c>
       <c r="R31" t="n">
-        <v>6972813</v>
+        <v>6972567</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,11 +3693,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3719,27 +3719,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126439884</v>
+        <v>126430999</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3748,16 +3748,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>593373</v>
+        <v>593357</v>
       </c>
       <c r="R32" t="n">
-        <v>6972785</v>
+        <v>6972730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,11 +3795,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,50 +4438,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126433556</v>
+        <v>126430758</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593175</v>
+        <v>593375</v>
       </c>
       <c r="R39" t="n">
-        <v>6972765</v>
+        <v>6972676</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,11 +4509,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4545,45 +4535,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126430758</v>
+        <v>126433556</v>
       </c>
       <c r="B40" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593375</v>
+        <v>593175</v>
       </c>
       <c r="R40" t="n">
-        <v>6972676</v>
+        <v>6972765</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4616,6 +4611,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5942,32 +5942,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126439869</v>
+        <v>126439895</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593194</v>
+        <v>593299</v>
       </c>
       <c r="R54" t="n">
-        <v>6972622</v>
+        <v>6972823</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6013,11 +6013,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6044,7 +6039,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126439868</v>
+        <v>126439869</v>
       </c>
       <c r="B55" t="n">
         <v>57657</v>
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>593219</v>
+        <v>593194</v>
       </c>
       <c r="R55" t="n">
-        <v>6972646</v>
+        <v>6972622</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6119,7 +6114,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6146,32 +6141,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126439895</v>
+        <v>126439868</v>
       </c>
       <c r="B56" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6181,10 +6176,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>593299</v>
+        <v>593219</v>
       </c>
       <c r="R56" t="n">
-        <v>6972823</v>
+        <v>6972646</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,6 +6212,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7156,7 +7156,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126431085</v>
+        <v>126439886</v>
       </c>
       <c r="B66" t="n">
         <v>57657</v>
@@ -7185,21 +7185,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>593369</v>
+        <v>593386</v>
       </c>
       <c r="R66" t="n">
-        <v>6972715</v>
+        <v>6972774</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7236,7 +7231,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7263,7 +7258,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126434333</v>
+        <v>126439874</v>
       </c>
       <c r="B67" t="n">
         <v>57657</v>
@@ -7292,21 +7287,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>593160</v>
+        <v>593158</v>
       </c>
       <c r="R67" t="n">
-        <v>6972621</v>
+        <v>6972739</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7343,7 +7333,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7370,7 +7360,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126439886</v>
+        <v>126431085</v>
       </c>
       <c r="B68" t="n">
         <v>57657</v>
@@ -7399,16 +7389,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>593386</v>
+        <v>593369</v>
       </c>
       <c r="R68" t="n">
-        <v>6972774</v>
+        <v>6972715</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7445,7 +7440,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7472,7 +7467,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126439874</v>
+        <v>126434333</v>
       </c>
       <c r="B69" t="n">
         <v>57657</v>
@@ -7501,16 +7496,21 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>593158</v>
+        <v>593160</v>
       </c>
       <c r="R69" t="n">
-        <v>6972739</v>
+        <v>6972621</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126434624</v>
+        <v>126439906</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593248</v>
+        <v>593425</v>
       </c>
       <c r="R11" t="n">
-        <v>6972573</v>
+        <v>6972739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126439906</v>
+        <v>126439876</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593425</v>
+        <v>593138</v>
       </c>
       <c r="R12" t="n">
-        <v>6972739</v>
+        <v>6972753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126439876</v>
+        <v>126434624</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593138</v>
+        <v>593248</v>
       </c>
       <c r="R13" t="n">
-        <v>6972753</v>
+        <v>6972573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126433726</v>
+        <v>126439904</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593198</v>
+        <v>593135</v>
       </c>
       <c r="R16" t="n">
-        <v>6972731</v>
+        <v>6972820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,11 +2174,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,27 +2200,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126439896</v>
+        <v>126433726</v>
       </c>
       <c r="B17" t="n">
-        <v>58027</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2240,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593366</v>
+        <v>593198</v>
       </c>
       <c r="R17" t="n">
-        <v>6972772</v>
+        <v>6972731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2276,6 +2271,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126439904</v>
+        <v>126439896</v>
       </c>
       <c r="B18" t="n">
-        <v>91263</v>
+        <v>58027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593135</v>
+        <v>593366</v>
       </c>
       <c r="R18" t="n">
-        <v>6972820</v>
+        <v>6972772</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,49 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126434180</v>
+        <v>126439893</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593208</v>
+        <v>593361</v>
       </c>
       <c r="R21" t="n">
-        <v>6972678</v>
+        <v>6972794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,45 +2700,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126439893</v>
+        <v>126434180</v>
       </c>
       <c r="B22" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593361</v>
+        <v>593208</v>
       </c>
       <c r="R22" t="n">
-        <v>6972794</v>
+        <v>6972678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126430580</v>
+        <v>126431424</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,39 +2812,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>593384</v>
+        <v>593306</v>
       </c>
       <c r="R23" t="n">
-        <v>6972679</v>
+        <v>6972805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,11 +2872,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på gran, äldre ringhack + äldre ringhack som har återanvänts.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,10 +2898,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126431424</v>
+        <v>126430580</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2919,34 +2909,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>593306</v>
+        <v>593384</v>
       </c>
       <c r="R24" t="n">
-        <v>6972805</v>
+        <v>6972679</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,6 +2974,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på gran, äldre ringhack + äldre ringhack som har återanvänts.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126439881</v>
+        <v>126434589</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3429,21 +3429,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>593155</v>
+        <v>593238</v>
       </c>
       <c r="R29" t="n">
-        <v>6972813</v>
+        <v>6972567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3489,11 +3489,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3520,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126439884</v>
+        <v>126439881</v>
       </c>
       <c r="B30" t="n">
         <v>57657</v>
@@ -3555,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>593373</v>
+        <v>593155</v>
       </c>
       <c r="R30" t="n">
-        <v>6972785</v>
+        <v>6972813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3622,10 +3617,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126434589</v>
+        <v>126439884</v>
       </c>
       <c r="B31" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,21 +3628,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3657,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>593238</v>
+        <v>593373</v>
       </c>
       <c r="R31" t="n">
-        <v>6972567</v>
+        <v>6972785</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3693,6 +3688,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3821,50 +3821,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126434241</v>
+        <v>126439898</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>593202</v>
+        <v>593306</v>
       </c>
       <c r="R33" t="n">
-        <v>6972629</v>
+        <v>6972813</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3901,7 +3896,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4030,7 +4025,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126439887</v>
+        <v>126434241</v>
       </c>
       <c r="B35" t="n">
         <v>57657</v>
@@ -4059,16 +4054,21 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>593434</v>
+        <v>593202</v>
       </c>
       <c r="R35" t="n">
-        <v>6972745</v>
+        <v>6972629</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,7 +4132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126432904</v>
+        <v>126439887</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>593235</v>
+        <v>593434</v>
       </c>
       <c r="R36" t="n">
-        <v>6972896</v>
+        <v>6972745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4234,7 +4234,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126439871</v>
+        <v>126432904</v>
       </c>
       <c r="B37" t="n">
         <v>57657</v>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>593164</v>
+        <v>593235</v>
       </c>
       <c r="R37" t="n">
-        <v>6972685</v>
+        <v>6972896</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4336,32 +4336,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126439898</v>
+        <v>126439871</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>593306</v>
+        <v>593164</v>
       </c>
       <c r="R38" t="n">
-        <v>6972813</v>
+        <v>6972685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4438,45 +4438,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126430758</v>
+        <v>126433556</v>
       </c>
       <c r="B39" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593375</v>
+        <v>593175</v>
       </c>
       <c r="R39" t="n">
-        <v>6972676</v>
+        <v>6972765</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4509,6 +4514,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4535,50 +4545,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126433556</v>
+        <v>126430758</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593175</v>
+        <v>593375</v>
       </c>
       <c r="R40" t="n">
-        <v>6972765</v>
+        <v>6972676</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,11 +4616,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4836,10 +4836,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126439867</v>
+        <v>126434119</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4847,34 +4847,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>593250</v>
+        <v>593241</v>
       </c>
       <c r="R43" t="n">
-        <v>6972866</v>
+        <v>6972676</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4907,6 +4912,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4943,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126434119</v>
+        <v>126439867</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,39 +4954,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>593241</v>
+        <v>593250</v>
       </c>
       <c r="R44" t="n">
-        <v>6972676</v>
+        <v>6972866</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5009,11 +5014,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5234,10 +5234,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126439905</v>
+        <v>126439883</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,21 +5245,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593134</v>
+        <v>593342</v>
       </c>
       <c r="R47" t="n">
-        <v>6972823</v>
+        <v>6972786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,6 +5305,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5331,10 +5336,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126439883</v>
+        <v>126439905</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,21 +5347,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5366,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>593342</v>
+        <v>593134</v>
       </c>
       <c r="R48" t="n">
-        <v>6972786</v>
+        <v>6972823</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5402,11 +5407,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126434358</v>
+        <v>126439882</v>
       </c>
       <c r="B50" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>593134</v>
+        <v>593280</v>
       </c>
       <c r="R50" t="n">
-        <v>6972597</v>
+        <v>6972844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5611,6 +5611,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5743,10 +5748,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126439882</v>
+        <v>126434358</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5754,21 +5759,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5778,10 +5783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>593280</v>
+        <v>593134</v>
       </c>
       <c r="R52" t="n">
-        <v>6972844</v>
+        <v>6972597</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5814,11 +5819,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5942,32 +5942,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126439895</v>
+        <v>126439869</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>593299</v>
+        <v>593194</v>
       </c>
       <c r="R54" t="n">
-        <v>6972823</v>
+        <v>6972622</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6013,6 +6013,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6039,7 +6044,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126439869</v>
+        <v>126439868</v>
       </c>
       <c r="B55" t="n">
         <v>57657</v>
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>593194</v>
+        <v>593219</v>
       </c>
       <c r="R55" t="n">
-        <v>6972622</v>
+        <v>6972646</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6114,7 +6119,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6141,32 +6146,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126439868</v>
+        <v>126439895</v>
       </c>
       <c r="B56" t="n">
-        <v>57657</v>
+        <v>80111</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6176,10 +6181,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>593219</v>
+        <v>593299</v>
       </c>
       <c r="R56" t="n">
-        <v>6972646</v>
+        <v>6972823</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,11 +6217,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6243,32 +6243,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126439889</v>
+        <v>126433598</v>
       </c>
       <c r="B57" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>593443</v>
+        <v>593170</v>
       </c>
       <c r="R57" t="n">
-        <v>6972717</v>
+        <v>6972741</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6314,11 +6314,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6345,7 +6340,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126439878</v>
+        <v>126439889</v>
       </c>
       <c r="B58" t="n">
         <v>57657</v>
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>593144</v>
+        <v>593443</v>
       </c>
       <c r="R58" t="n">
-        <v>6972760</v>
+        <v>6972717</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6420,7 +6415,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6447,7 +6442,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126439873</v>
+        <v>126439878</v>
       </c>
       <c r="B59" t="n">
         <v>57657</v>
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>593152</v>
+        <v>593144</v>
       </c>
       <c r="R59" t="n">
-        <v>6972714</v>
+        <v>6972760</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6549,32 +6544,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126433598</v>
+        <v>126439873</v>
       </c>
       <c r="B60" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>593170</v>
+        <v>593152</v>
       </c>
       <c r="R60" t="n">
-        <v>6972741</v>
+        <v>6972714</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,6 +6615,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6646,10 +6646,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126434452</v>
+        <v>126439901</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6657,21 +6657,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>593205</v>
+        <v>593249</v>
       </c>
       <c r="R61" t="n">
-        <v>6972593</v>
+        <v>6972870</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6717,11 +6717,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6748,10 +6743,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126439901</v>
+        <v>126434452</v>
       </c>
       <c r="B62" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6759,21 +6754,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6783,10 +6778,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>593249</v>
+        <v>593205</v>
       </c>
       <c r="R62" t="n">
-        <v>6972870</v>
+        <v>6972593</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6819,6 +6814,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Riklig förekomst inom området</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6947,10 +6947,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126434201</v>
+        <v>126433689</v>
       </c>
       <c r="B64" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,27 +6958,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>593201</v>
+        <v>593188</v>
       </c>
       <c r="R64" t="n">
-        <v>6972667</v>
+        <v>6972729</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7023,6 +7023,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7049,7 +7054,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126433689</v>
+        <v>126431085</v>
       </c>
       <c r="B65" t="n">
         <v>57657</v>
@@ -7085,14 +7090,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>593188</v>
+        <v>593369</v>
       </c>
       <c r="R65" t="n">
-        <v>6972729</v>
+        <v>6972715</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7129,7 +7134,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7156,7 +7161,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126439886</v>
+        <v>126434333</v>
       </c>
       <c r="B66" t="n">
         <v>57657</v>
@@ -7185,16 +7190,21 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>593386</v>
+        <v>593160</v>
       </c>
       <c r="R66" t="n">
-        <v>6972774</v>
+        <v>6972621</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7231,7 +7241,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7258,7 +7268,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126439874</v>
+        <v>126439886</v>
       </c>
       <c r="B67" t="n">
         <v>57657</v>
@@ -7293,10 +7303,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>593158</v>
+        <v>593386</v>
       </c>
       <c r="R67" t="n">
-        <v>6972739</v>
+        <v>6972774</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7360,7 +7370,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126431085</v>
+        <v>126439874</v>
       </c>
       <c r="B68" t="n">
         <v>57657</v>
@@ -7389,21 +7399,16 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>593369</v>
+        <v>593158</v>
       </c>
       <c r="R68" t="n">
-        <v>6972715</v>
+        <v>6972739</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7440,7 +7445,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7467,10 +7472,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126434333</v>
+        <v>126434201</v>
       </c>
       <c r="B69" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7478,27 +7483,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7507,10 +7512,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>593160</v>
+        <v>593201</v>
       </c>
       <c r="R69" t="n">
-        <v>6972621</v>
+        <v>6972667</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7543,11 +7548,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126439906</v>
+        <v>126439876</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593425</v>
+        <v>593138</v>
       </c>
       <c r="R11" t="n">
-        <v>6972739</v>
+        <v>6972753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126439876</v>
+        <v>126434624</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593138</v>
+        <v>593248</v>
       </c>
       <c r="R12" t="n">
-        <v>6972753</v>
+        <v>6972573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1781,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126434624</v>
+        <v>126439906</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593248</v>
+        <v>593425</v>
       </c>
       <c r="R13" t="n">
-        <v>6972573</v>
+        <v>6972739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2603,45 +2603,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126439893</v>
+        <v>126434180</v>
       </c>
       <c r="B21" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593361</v>
+        <v>593208</v>
       </c>
       <c r="R21" t="n">
-        <v>6972794</v>
+        <v>6972678</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,49 +2704,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126434180</v>
+        <v>126439893</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593208</v>
+        <v>593361</v>
       </c>
       <c r="R22" t="n">
-        <v>6972678</v>
+        <v>6972794</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4438,50 +4438,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126433556</v>
+        <v>126430758</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593175</v>
+        <v>593375</v>
       </c>
       <c r="R39" t="n">
-        <v>6972765</v>
+        <v>6972676</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4514,11 +4509,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4545,45 +4535,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126430758</v>
+        <v>126432147</v>
       </c>
       <c r="B40" t="n">
-        <v>98278</v>
+        <v>91263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593375</v>
+        <v>593250</v>
       </c>
       <c r="R40" t="n">
-        <v>6972676</v>
+        <v>6972871</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,7 +4632,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126432147</v>
+        <v>126431305</v>
       </c>
       <c r="B41" t="n">
         <v>91263</v>
@@ -4673,14 +4663,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593250</v>
+        <v>593333</v>
       </c>
       <c r="R41" t="n">
-        <v>6972871</v>
+        <v>6972791</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,10 +4729,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126431305</v>
+        <v>126433556</v>
       </c>
       <c r="B42" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4750,34 +4740,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593333</v>
+        <v>593175</v>
       </c>
       <c r="R42" t="n">
-        <v>6972791</v>
+        <v>6972765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4810,6 +4805,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6243,32 +6243,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126433598</v>
+        <v>126439889</v>
       </c>
       <c r="B57" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>593170</v>
+        <v>593443</v>
       </c>
       <c r="R57" t="n">
-        <v>6972741</v>
+        <v>6972717</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6314,6 +6314,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6340,7 +6345,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126439889</v>
+        <v>126439878</v>
       </c>
       <c r="B58" t="n">
         <v>57657</v>
@@ -6375,10 +6380,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>593443</v>
+        <v>593144</v>
       </c>
       <c r="R58" t="n">
-        <v>6972717</v>
+        <v>6972760</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6415,7 +6420,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6442,7 +6447,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126439878</v>
+        <v>126439873</v>
       </c>
       <c r="B59" t="n">
         <v>57657</v>
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>593144</v>
+        <v>593152</v>
       </c>
       <c r="R59" t="n">
-        <v>6972760</v>
+        <v>6972714</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6544,32 +6549,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126439873</v>
+        <v>126433598</v>
       </c>
       <c r="B60" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>593152</v>
+        <v>593170</v>
       </c>
       <c r="R60" t="n">
-        <v>6972714</v>
+        <v>6972741</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,11 +6620,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -2603,49 +2603,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126434180</v>
+        <v>126439893</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>593208</v>
+        <v>593361</v>
       </c>
       <c r="R21" t="n">
-        <v>6972678</v>
+        <v>6972794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,45 +2700,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126439893</v>
+        <v>126434180</v>
       </c>
       <c r="B22" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>593361</v>
+        <v>593208</v>
       </c>
       <c r="R22" t="n">
-        <v>6972794</v>
+        <v>6972678</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126439883</v>
+        <v>126439905</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,21 +5245,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593342</v>
+        <v>593134</v>
       </c>
       <c r="R47" t="n">
-        <v>6972786</v>
+        <v>6972823</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,11 +5305,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5336,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126439905</v>
+        <v>126439883</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,21 +5342,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>593134</v>
+        <v>593342</v>
       </c>
       <c r="R48" t="n">
-        <v>6972823</v>
+        <v>6972786</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5407,6 +5402,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126439882</v>
+        <v>126434358</v>
       </c>
       <c r="B50" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>593280</v>
+        <v>593134</v>
       </c>
       <c r="R50" t="n">
-        <v>6972844</v>
+        <v>6972597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5611,11 +5611,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,49 +5637,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126430873</v>
+        <v>126439882</v>
       </c>
       <c r="B51" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>593384</v>
+        <v>593280</v>
       </c>
       <c r="R51" t="n">
-        <v>6972679</v>
+        <v>6972844</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5721,7 +5712,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Riklig förekomst av dom</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5748,45 +5739,49 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126434358</v>
+        <v>126430873</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>98382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>593134</v>
+        <v>593384</v>
       </c>
       <c r="R52" t="n">
-        <v>6972597</v>
+        <v>6972679</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5819,6 +5814,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av dom</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 26392-2025 artfynd.xlsx
+++ b/artfynd/A 26392-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126439876</v>
+        <v>126439906</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593138</v>
+        <v>593425</v>
       </c>
       <c r="R11" t="n">
-        <v>6972753</v>
+        <v>6972739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,11 +1679,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126434624</v>
+        <v>126439876</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593248</v>
+        <v>593138</v>
       </c>
       <c r="R12" t="n">
-        <v>6972573</v>
+        <v>6972753</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126439906</v>
+        <v>126434624</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593425</v>
+        <v>593248</v>
       </c>
       <c r="R13" t="n">
-        <v>6972739</v>
+        <v>6972573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -4438,45 +4438,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126430758</v>
+        <v>126433556</v>
       </c>
       <c r="B39" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>593375</v>
+        <v>593175</v>
       </c>
       <c r="R39" t="n">
-        <v>6972676</v>
+        <v>6972765</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4509,6 +4514,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4535,45 +4545,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126432147</v>
+        <v>126430758</v>
       </c>
       <c r="B40" t="n">
-        <v>91263</v>
+        <v>98278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>593250</v>
+        <v>593375</v>
       </c>
       <c r="R40" t="n">
-        <v>6972871</v>
+        <v>6972676</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4632,7 +4642,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126431305</v>
+        <v>126432147</v>
       </c>
       <c r="B41" t="n">
         <v>91263</v>
@@ -4663,14 +4673,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>593333</v>
+        <v>593250</v>
       </c>
       <c r="R41" t="n">
-        <v>6972791</v>
+        <v>6972871</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,10 +4739,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126433556</v>
+        <v>126431305</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4740,39 +4750,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>593175</v>
+        <v>593333</v>
       </c>
       <c r="R42" t="n">
-        <v>6972765</v>
+        <v>6972791</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4805,11 +4810,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5234,10 +5234,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126439905</v>
+        <v>126439883</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5245,21 +5245,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>593134</v>
+        <v>593342</v>
       </c>
       <c r="R47" t="n">
-        <v>6972823</v>
+        <v>6972786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5305,6 +5305,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5331,10 +5336,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126439883</v>
+        <v>126439905</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5342,21 +5347,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5366,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>593342</v>
+        <v>593134</v>
       </c>
       <c r="R48" t="n">
-        <v>6972786</v>
+        <v>6972823</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5402,11 +5407,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5540,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126434358</v>
+        <v>126439882</v>
       </c>
       <c r="B50" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5551,21 +5551,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>593134</v>
+        <v>593280</v>
       </c>
       <c r="R50" t="n">
-        <v>6972597</v>
+        <v>6972844</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5611,6 +5611,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5637,45 +5642,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126439882</v>
+        <v>126430873</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fisklössjön, Mpd</t>
+          <t>Fisklössjöflon, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>593280</v>
+        <v>593384</v>
       </c>
       <c r="R51" t="n">
-        <v>6972844</v>
+        <v>6972679</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5712,7 +5721,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Riklig förekomst av dom</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5739,49 +5748,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126430873</v>
+        <v>126434358</v>
       </c>
       <c r="B52" t="n">
-        <v>98382</v>
+        <v>91245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fisklössjöflon, Mpd</t>
+          <t>Fisklössjön, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>593384</v>
+        <v>593134</v>
       </c>
       <c r="R52" t="n">
-        <v>6972679</v>
+        <v>6972597</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5814,11 +5819,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av dom</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6243,32 +6243,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126439889</v>
+        <v>126433598</v>
       </c>
       <c r="B57" t="n">
-        <v>57657</v>
+        <v>98278</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>593443</v>
+        <v>593170</v>
       </c>
       <c r="R57" t="n">
-        <v>6972717</v>
+        <v>6972741</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6314,11 +6314,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6345,7 +6340,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126439878</v>
+        <v>126439889</v>
       </c>
       <c r="B58" t="n">
         <v>57657</v>
@@ -6380,10 +6375,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>593144</v>
+        <v>593443</v>
       </c>
       <c r="R58" t="n">
-        <v>6972760</v>
+        <v>6972717</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6420,7 +6415,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6447,7 +6442,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126439873</v>
+        <v>126439878</v>
       </c>
       <c r="B59" t="n">
         <v>57657</v>
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>593152</v>
+        <v>593144</v>
       </c>
       <c r="R59" t="n">
-        <v>6972714</v>
+        <v>6972760</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6549,32 +6544,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126433598</v>
+        <v>126439873</v>
       </c>
       <c r="B60" t="n">
-        <v>98278</v>
+        <v>57657</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>593170</v>
+        <v>593152</v>
       </c>
       <c r="R60" t="n">
-        <v>6972741</v>
+        <v>6972714</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,6 +6615,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
